--- a/data/metadata_raw/regional_gdp.xlsx
+++ b/data/metadata_raw/regional_gdp.xlsx
@@ -527,7 +527,7 @@
     <t>2022-08-08</t>
   </si>
   <si>
-    <t>2025-08-15</t>
+    <t>2026-01-27</t>
   </si>
   <si>
     <t>1.01.03.0001</t>
